--- a/feedback_surveys/012_exam_process_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/012_exam_process_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied',_'value':_5}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied', 'value': 5}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied',_'value':_4}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat satisfied', 'value': 4}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_dissatisfied',_'value':_3}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat dissatisfied', 'value': 3}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -745,29 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_dissatisfied',_'value':_2}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very dissatisfied', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Very dissatisfied', 'value': 1}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
